--- a/docs/measured/oufuku-shinki.xlsx
+++ b/docs/measured/oufuku-shinki.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D26"/>
   <sheetData>
     <row r="1">
       <c r="A1">
@@ -573,9 +573,27 @@
         <v/>
       </c>
     </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <f>YEARFRAC(DATE(2008,10,15),DATE(2009,3,1),1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <f>YEARFRAC(DATE(2008,3,1),DATE(2009,3,2),1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <f>YEARFRAC(DATE(2008,1,15),DATE(2008,6,30),1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D26"/>
   </ignoredErrors>
 </worksheet>
 </file>